--- a/Collections/Germany/#Germany#FRG#Regular#[1948-2001]#circulation_quality.xlsx
+++ b/Collections/Germany/#Germany#FRG#Regular#[1948-2001]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Germany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8219D7AB-AA1C-46B0-9520-C0B2B4D6416F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A54C153-2728-43FF-8720-73D1B2B11F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1₰" sheetId="12" r:id="rId1"/>
@@ -43,6 +43,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -7068,7 +7071,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7420,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7552,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="12" t="str">
         <f t="shared" si="1"/>
@@ -7634,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
@@ -7722,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -10113,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="3">
         <v>0</v>
@@ -10389,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="3">
         <v>0</v>
@@ -10803,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="3">
         <v>0</v>
@@ -10941,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="3">
         <v>0</v>
@@ -14587,13 +14590,13 @@
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="3">
         <v>0</v>
@@ -14604,7 +14607,7 @@
       </c>
       <c r="AL6" s="8">
         <f t="shared" ref="AL6:AL27" si="2">SUM(A6:M6)</f>
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="AM6" s="8">
         <f t="shared" ref="AM6:AM27" si="3">PRODUCT(A6:M6)</f>
@@ -16889,7 +16892,7 @@
         <v>0</v>
       </c>
       <c r="N46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="12" t="str">
         <f t="shared" si="0"/>
@@ -16936,7 +16939,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -16953,7 +16956,7 @@
       </c>
       <c r="AL47" s="8">
         <f t="shared" si="4"/>
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="AM47" s="8">
         <f t="shared" si="5"/>
@@ -17001,7 +17004,7 @@
         <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="12" t="str">
         <f t="shared" si="0"/>
@@ -17048,7 +17051,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -17065,7 +17068,7 @@
       </c>
       <c r="AL49" s="8">
         <f t="shared" si="4"/>
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="AM49" s="8">
         <f t="shared" si="5"/>
@@ -19476,7 +19479,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -19936,7 +19939,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -22599,7 +22602,7 @@
         <v>711</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
